--- a/2025/ЗАВОДЫ/Черкизово UZ/2025/12,25/11,12,25 Черкизово Ташкент/дв 11,12,25 тшрсч чркзв НОВИНКИ.xlsx
+++ b/2025/ЗАВОДЫ/Черкизово UZ/2025/12,25/11,12,25 Черкизово Ташкент/дв 11,12,25 тшрсч чркзв НОВИНКИ.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\ЗАВОДЫ\Черкизово UZ\2025\12,25\11,12,25 Черкизово Ташкент\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\2025\ЗАВОДЫ\Черкизово UZ\2025\12,25\11,12,25 Черкизово Ташкент\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6697458C-D67D-40AA-97FE-6C1592EE40B6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73FCE2C9-2164-42E2-A0EB-FBE827FBCF38}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -217,17 +217,23 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <strike/>
@@ -238,7 +244,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -288,6 +294,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -364,7 +376,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -381,11 +393,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="10" borderId="3" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1915,12 +1928,12 @@
       <c r="P6" s="7">
         <v>0</v>
       </c>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20">
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18">
         <f>IFERROR(VLOOKUP(I6,[1]Sheet!$I:$R,10,0),0)</f>
         <v>200</v>
       </c>
-      <c r="S6" s="20"/>
+      <c r="S6" s="18"/>
       <c r="T6" s="7"/>
       <c r="U6" s="7"/>
       <c r="V6" s="7"/>
@@ -1976,7 +1989,7 @@
       <c r="AY6" s="7"/>
     </row>
     <row r="7" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="21" t="s">
         <v>39</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -1989,7 +2002,7 @@
       <c r="G7" s="8">
         <v>1.5</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="16">
         <v>31</v>
       </c>
       <c r="I7" s="7">
@@ -2004,12 +2017,12 @@
       <c r="P7" s="7">
         <v>0</v>
       </c>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20">
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18">
         <f>IFERROR(VLOOKUP(I7,[1]Sheet!$I:$R,10,0),0)</f>
         <v>6</v>
       </c>
-      <c r="S7" s="20"/>
+      <c r="S7" s="18"/>
       <c r="T7" s="7"/>
       <c r="U7" s="7"/>
       <c r="V7" s="7"/>
@@ -2065,7 +2078,7 @@
       <c r="AY7" s="7"/>
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="19" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -2093,12 +2106,12 @@
       <c r="P8" s="7">
         <v>0</v>
       </c>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20">
+      <c r="Q8" s="18"/>
+      <c r="R8" s="18">
         <f>IFERROR(VLOOKUP(I8,[1]Sheet!$I:$R,10,0),0)</f>
         <v>60</v>
       </c>
-      <c r="S8" s="20"/>
+      <c r="S8" s="18"/>
       <c r="T8" s="7"/>
       <c r="U8" s="7"/>
       <c r="V8" s="7"/>
@@ -2154,7 +2167,7 @@
       <c r="AY8" s="7"/>
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="19" t="s">
         <v>41</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -2182,12 +2195,12 @@
       <c r="P9" s="7">
         <v>0</v>
       </c>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20">
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18">
         <f>IFERROR(VLOOKUP(I9,[1]Sheet!$I:$R,10,0),0)</f>
         <v>50</v>
       </c>
-      <c r="S9" s="20"/>
+      <c r="S9" s="18"/>
       <c r="T9" s="7"/>
       <c r="U9" s="7"/>
       <c r="V9" s="7"/>
@@ -2243,7 +2256,7 @@
       <c r="AY9" s="7"/>
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="19" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="7" t="s">
@@ -2271,12 +2284,12 @@
       <c r="P10" s="7">
         <v>0</v>
       </c>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20">
+      <c r="Q10" s="18"/>
+      <c r="R10" s="18">
         <f>IFERROR(VLOOKUP(I10,[1]Sheet!$I:$R,10,0),0)</f>
         <v>50</v>
       </c>
-      <c r="S10" s="20"/>
+      <c r="S10" s="18"/>
       <c r="T10" s="7"/>
       <c r="U10" s="7"/>
       <c r="V10" s="7"/>
@@ -2332,7 +2345,7 @@
       <c r="AY10" s="7"/>
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="19" t="s">
         <v>43</v>
       </c>
       <c r="B11" s="7" t="s">
@@ -2360,12 +2373,12 @@
       <c r="P11" s="7">
         <v>0</v>
       </c>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20">
+      <c r="Q11" s="18"/>
+      <c r="R11" s="18">
         <f>IFERROR(VLOOKUP(I11,[1]Sheet!$I:$R,10,0),0)</f>
         <v>80</v>
       </c>
-      <c r="S11" s="20"/>
+      <c r="S11" s="18"/>
       <c r="T11" s="7"/>
       <c r="U11" s="7"/>
       <c r="V11" s="7"/>
@@ -2421,7 +2434,7 @@
       <c r="AY11" s="7"/>
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
+      <c r="A12" s="19" t="s">
         <v>44</v>
       </c>
       <c r="B12" s="7" t="s">
@@ -2449,12 +2462,12 @@
       <c r="P12" s="7">
         <v>0</v>
       </c>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20">
+      <c r="Q12" s="18"/>
+      <c r="R12" s="18">
         <f>IFERROR(VLOOKUP(I12,[1]Sheet!$I:$R,10,0),0)</f>
         <v>40</v>
       </c>
-      <c r="S12" s="20"/>
+      <c r="S12" s="18"/>
       <c r="T12" s="7"/>
       <c r="U12" s="7"/>
       <c r="V12" s="7"/>
@@ -2510,7 +2523,7 @@
       <c r="AY12" s="7"/>
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="17" t="s">
         <v>45</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -2523,7 +2536,7 @@
       <c r="G13" s="8">
         <v>0.35</v>
       </c>
-      <c r="H13" s="17">
+      <c r="H13" s="16">
         <v>31</v>
       </c>
       <c r="I13" s="15">
@@ -2538,12 +2551,12 @@
       <c r="P13" s="7">
         <v>0</v>
       </c>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20">
+      <c r="Q13" s="18"/>
+      <c r="R13" s="18">
         <f>IFERROR(VLOOKUP(I13,[1]Sheet!$I:$R,10,0),0)</f>
         <v>5</v>
       </c>
-      <c r="S13" s="20"/>
+      <c r="S13" s="18"/>
       <c r="T13" s="7"/>
       <c r="U13" s="7"/>
       <c r="V13" s="7"/>
@@ -2599,7 +2612,7 @@
       <c r="AY13" s="7"/>
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="19" t="s">
         <v>46</v>
       </c>
       <c r="B14" s="7" t="s">
@@ -2612,7 +2625,7 @@
       <c r="G14" s="8">
         <v>0.4</v>
       </c>
-      <c r="H14" s="17">
+      <c r="H14" s="16">
         <v>45</v>
       </c>
       <c r="I14" s="15">
@@ -2627,12 +2640,12 @@
       <c r="P14" s="7">
         <v>0</v>
       </c>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20">
+      <c r="Q14" s="18"/>
+      <c r="R14" s="18">
         <f>IFERROR(VLOOKUP(I14,[1]Sheet!$I:$R,10,0),0)</f>
         <v>10</v>
       </c>
-      <c r="S14" s="20"/>
+      <c r="S14" s="18"/>
       <c r="T14" s="7"/>
       <c r="U14" s="7"/>
       <c r="V14" s="7"/>
@@ -2688,7 +2701,7 @@
       <c r="AY14" s="7"/>
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>47</v>
       </c>
       <c r="B15" s="7" t="s">
@@ -2716,12 +2729,12 @@
       <c r="P15" s="7">
         <v>0</v>
       </c>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20">
+      <c r="Q15" s="18"/>
+      <c r="R15" s="18">
         <f>IFERROR(VLOOKUP(I15,[1]Sheet!$I:$R,10,0),0)</f>
         <v>40</v>
       </c>
-      <c r="S15" s="20"/>
+      <c r="S15" s="18"/>
       <c r="T15" s="7"/>
       <c r="U15" s="7"/>
       <c r="V15" s="7"/>
@@ -2777,7 +2790,7 @@
       <c r="AY15" s="7"/>
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="19" t="s">
         <v>48</v>
       </c>
       <c r="B16" s="7" t="s">
@@ -2790,7 +2803,7 @@
       <c r="G16" s="8">
         <v>0.4</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="16">
         <v>40</v>
       </c>
       <c r="I16" s="15">
@@ -2805,12 +2818,12 @@
       <c r="P16" s="7">
         <v>0</v>
       </c>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20">
+      <c r="Q16" s="18"/>
+      <c r="R16" s="18">
         <f>IFERROR(VLOOKUP(I16,[1]Sheet!$I:$R,10,0),0)</f>
         <v>5</v>
       </c>
-      <c r="S16" s="20"/>
+      <c r="S16" s="18"/>
       <c r="T16" s="7"/>
       <c r="U16" s="7"/>
       <c r="V16" s="7"/>
@@ -2866,7 +2879,7 @@
       <c r="AY16" s="7"/>
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
         <v>49</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -2894,12 +2907,12 @@
       <c r="P17" s="7">
         <v>0</v>
       </c>
-      <c r="Q17" s="20"/>
-      <c r="R17" s="20">
+      <c r="Q17" s="18"/>
+      <c r="R17" s="18">
         <f>IFERROR(VLOOKUP(I17,[1]Sheet!$I:$R,10,0),0)</f>
         <v>40</v>
       </c>
-      <c r="S17" s="20"/>
+      <c r="S17" s="18"/>
       <c r="T17" s="7"/>
       <c r="U17" s="7"/>
       <c r="V17" s="7"/>
@@ -2955,7 +2968,7 @@
       <c r="AY17" s="7"/>
     </row>
     <row r="18" spans="1:51" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="20" t="s">
         <v>50</v>
       </c>
       <c r="B18" s="7" t="s">
@@ -2983,12 +2996,12 @@
       <c r="P18" s="7">
         <v>0</v>
       </c>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="20">
+      <c r="Q18" s="18"/>
+      <c r="R18" s="18">
         <f>IFERROR(VLOOKUP(I18,[1]Sheet!$I:$R,10,0),0)</f>
         <v>120</v>
       </c>
-      <c r="S18" s="20"/>
+      <c r="S18" s="18"/>
       <c r="T18" s="7"/>
       <c r="U18" s="7"/>
       <c r="V18" s="7"/>
